--- a/docs/design-docs/13_DB設計書.xlsx
+++ b/docs/design-docs/13_DB設計書.xlsx
@@ -10,7 +10,575 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>データベース設計書</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>DBMS</t>
+  </si>
+  <si>
+    <t>H2 Database 1.4.200（ファイルモード）</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-DB-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>文字コード</t>
+  </si>
+  <si>
+    <t>UTF-8</t>
+  </si>
+  <si>
+    <t>接続モード</t>
+  </si>
+  <si>
+    <t>ファイル（./struts-lab-db）</t>
+  </si>
+  <si>
+    <t>equipment (設備マスタ)</t>
+  </si>
+  <si>
+    <t>カラム名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>制約</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>equipment_code</t>
+  </si>
+  <si>
+    <t>VARCHAR(20)</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>設備コード</t>
+  </si>
+  <si>
+    <t>equipment_name</t>
+  </si>
+  <si>
+    <t>VARCHAR(100)</t>
+  </si>
+  <si>
+    <t>NOT NULL</t>
+  </si>
+  <si>
+    <t>設備名</t>
+  </si>
+  <si>
+    <t>equipment_type</t>
+  </si>
+  <si>
+    <t>VARCHAR(10)</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>voltage_level</t>
+  </si>
+  <si>
+    <t>電圧階級</t>
+  </si>
+  <si>
+    <t>parent_equipment_code</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>親設備（自己参照）</t>
+  </si>
+  <si>
+    <t>maintenance_rank</t>
+  </si>
+  <si>
+    <t>CHAR(1)</t>
+  </si>
+  <si>
+    <t>S/A/B/C</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>VARCHAR(5)</t>
+  </si>
+  <si>
+    <t>運用中/停止中/廃止</t>
+  </si>
+  <si>
+    <t>inspection_template (点検項目テンプレート)</t>
+  </si>
+  <si>
+    <t>template_id</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>PK AUTO</t>
+  </si>
+  <si>
+    <t>templateID</t>
+  </si>
+  <si>
+    <t>template_name</t>
+  </si>
+  <si>
+    <t>template名</t>
+  </si>
+  <si>
+    <t>対象設備種別</t>
+  </si>
+  <si>
+    <t>inspection_kind</t>
+  </si>
+  <si>
+    <t>日常/定期/精密</t>
+  </si>
+  <si>
+    <t>inspection_items (点検項目3階層)</t>
+  </si>
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>項目ID</t>
+  </si>
+  <si>
+    <t>FK→inspection_template</t>
+  </si>
+  <si>
+    <t>parent_item_id</t>
+  </si>
+  <si>
+    <t>FK→inspection_items</t>
+  </si>
+  <si>
+    <t>親項目（自己参照）</t>
+  </si>
+  <si>
+    <t>item_level</t>
+  </si>
+  <si>
+    <t>1=大分類/2=中分類/3=個別</t>
+  </si>
+  <si>
+    <t>item_name</t>
+  </si>
+  <si>
+    <t>VARCHAR(200)</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>inspection_plans (点検計画)</t>
+  </si>
+  <si>
+    <t>plan_id</t>
+  </si>
+  <si>
+    <t>計画ID</t>
+  </si>
+  <si>
+    <t>fiscal_year</t>
+  </si>
+  <si>
+    <t>VARCHAR(4)</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>FK→equipment</t>
+  </si>
+  <si>
+    <t>対象設備</t>
+  </si>
+  <si>
+    <t>planned_date</t>
+  </si>
+  <si>
+    <t>VARCHAR(8)</t>
+  </si>
+  <si>
+    <t>点検予定日</t>
+  </si>
+  <si>
+    <t>予定/実施済/中止/延期</t>
+  </si>
+  <si>
+    <t>is_locked</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>計画lock</t>
+  </si>
+  <si>
+    <t>inspection_results (点検実施ヘッダ)</t>
+  </si>
+  <si>
+    <t>result_id</t>
+  </si>
+  <si>
+    <t>結果ID</t>
+  </si>
+  <si>
+    <t>FK→inspection_plans</t>
+  </si>
+  <si>
+    <t>executed_date</t>
+  </si>
+  <si>
+    <t>実施日</t>
+  </si>
+  <si>
+    <t>summary_judge</t>
+  </si>
+  <si>
+    <t>NORMAL/ABNORMAL/WATCH</t>
+  </si>
+  <si>
+    <t>approval_status</t>
+  </si>
+  <si>
+    <t>申請中/承認済/差戻</t>
+  </si>
+  <si>
+    <t>incidents (異常報告)</t>
+  </si>
+  <si>
+    <t>incident_no</t>
+  </si>
+  <si>
+    <t>INC-YYYYMMDD-NNN</t>
+  </si>
+  <si>
+    <t>incident_type</t>
+  </si>
+  <si>
+    <t>異常種別</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>軽微/中/重大/緊急</t>
+  </si>
+  <si>
+    <t>未了/調査中/対応中/完了/CAPA/close</t>
+  </si>
+  <si>
+    <t>counter_orders (対応指示ヘッダ)</t>
+  </si>
+  <si>
+    <t>order_no</t>
+  </si>
+  <si>
+    <t>CTR-YYYYMMDD-NNN</t>
+  </si>
+  <si>
+    <t>FK→incidents</t>
+  </si>
+  <si>
+    <t>未了/処理中/完了</t>
+  </si>
+  <si>
+    <t>counter_order_details (対応指示明細)</t>
+  </si>
+  <si>
+    <t>detail_id</t>
+  </si>
+  <si>
+    <t>FK→counter_orders</t>
+  </si>
+  <si>
+    <t>seq_no</t>
+  </si>
+  <si>
+    <t>行番号</t>
+  </si>
+  <si>
+    <t>work_content</t>
+  </si>
+  <si>
+    <t>VARCHAR(500)</t>
+  </si>
+  <si>
+    <t>作業内容</t>
+  </si>
+  <si>
+    <t>VARCHAR(3)</t>
+  </si>
+  <si>
+    <t>未了/完了</t>
+  </si>
+  <si>
+    <t>departments (部署マスタ)</t>
+  </si>
+  <si>
+    <t>dept_code</t>
+  </si>
+  <si>
+    <t>部署code</t>
+  </si>
+  <si>
+    <t>dept_name</t>
+  </si>
+  <si>
+    <t>部署名</t>
+  </si>
+  <si>
+    <t>parent_dept_code</t>
+  </si>
+  <si>
+    <t>FK→departments</t>
+  </si>
+  <si>
+    <t>上位部署</t>
+  </si>
+  <si>
+    <t>dept_level</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>dept_type</t>
+  </si>
+  <si>
+    <t>本社/支社/営業所/出張所</t>
+  </si>
+  <si>
+    <t>employees (担当者マスタ)</t>
+  </si>
+  <si>
+    <t>emp_no</t>
+  </si>
+  <si>
+    <t>EMP-NNNN</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>氏名</t>
+  </si>
+  <si>
+    <t>所属部署</t>
+  </si>
+  <si>
+    <t>login_id</t>
+  </si>
+  <si>
+    <t>VARCHAR(50)</t>
+  </si>
+  <si>
+    <t>NOT NULL UNIQUE</t>
+  </si>
+  <si>
+    <t>loginID</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+  </si>
+  <si>
+    <t>VARCHAR(64)</t>
+  </si>
+  <si>
+    <t>SHA-256</t>
+  </si>
+  <si>
+    <t>holidays (休日マスタ)</t>
+  </si>
+  <si>
+    <t>holiday_id</t>
+  </si>
+  <si>
+    <t>holiday_date</t>
+  </si>
+  <si>
+    <t>日付</t>
+  </si>
+  <si>
+    <t>holiday_type</t>
+  </si>
+  <si>
+    <t>法定/会社指定/点検停止</t>
+  </si>
+  <si>
+    <t>parts (保守部品マスタ)</t>
+  </si>
+  <si>
+    <t>part_code</t>
+  </si>
+  <si>
+    <t>部品code</t>
+  </si>
+  <si>
+    <t>part_name</t>
+  </si>
+  <si>
+    <t>部品名</t>
+  </si>
+  <si>
+    <t>current_stock</t>
+  </si>
+  <si>
+    <t>現在庫数</t>
+  </si>
+  <si>
+    <t>order_point</t>
+  </si>
+  <si>
+    <t>発注点</t>
+  </si>
+  <si>
+    <t>safety_stock</t>
+  </si>
+  <si>
+    <t>安全在庫数</t>
+  </si>
+  <si>
+    <t>part_usages (部品使用実績)</t>
+  </si>
+  <si>
+    <t>usage_id</t>
+  </si>
+  <si>
+    <t>FK→parts</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>使用量</t>
+  </si>
+  <si>
+    <t>stock_before</t>
+  </si>
+  <si>
+    <t>使用前在庫</t>
+  </si>
+  <si>
+    <t>stock_after</t>
+  </si>
+  <si>
+    <t>使用後在庫</t>
+  </si>
+  <si>
+    <t>主要リレーション</t>
+  </si>
+  <si>
+    <t>equipment.parent_equipment_code → equipment.equipment_code</t>
+  </si>
+  <si>
+    <t>inspection_items.template_id → inspection_template.template_id</t>
+  </si>
+  <si>
+    <t>inspection_items.parent_item_id → inspection_items.item_id</t>
+  </si>
+  <si>
+    <t>inspection_plans.equipment_code → equipment.equipment_code</t>
+  </si>
+  <si>
+    <t>inspection_results.plan_id → inspection_plans.plan_id</t>
+  </si>
+  <si>
+    <t>incidents.equipment_code → equipment.equipment_code</t>
+  </si>
+  <si>
+    <t>incident_timeline.incident_no → incidents.incident_no</t>
+  </si>
+  <si>
+    <t>counter_orders.incident_no → incidents.incident_no</t>
+  </si>
+  <si>
+    <t>counter_order_details.order_no → counter_orders.order_no</t>
+  </si>
+  <si>
+    <t>departments.parent_dept_code → departments.dept_code</t>
+  </si>
+  <si>
+    <t>employees.dept_code → departments.dept_code</t>
+  </si>
+  <si>
+    <t>part_usages.part_code → parts.part_code</t>
+  </si>
+  <si>
+    <t>part_usages.equipment_code → equipment.equipment_code</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
